--- a/sheets/조재수대금교본/검수/조재수의 이별 그리고 그리움.xlsx
+++ b/sheets/조재수대금교본/검수/조재수의 이별 그리고 그리움.xlsx
@@ -8648,7 +8648,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -8661,7 +8661,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -8674,7 +8674,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -8687,7 +8687,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -8700,7 +8700,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -8788,7 +8788,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G6" s="22"/>
@@ -8800,7 +8800,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -8817,22 +8817,18 @@
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
       <c r="S6" s="22"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -8880,50 +8876,25 @@
     </row>
     <row r="8" ht="106.4" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
       <c r="D8" s="21"/>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
@@ -8932,12 +8903,7 @@
         </is>
       </c>
       <c r="S8" s="24"/>
-      <c r="T8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="T8" s="21"/>
       <c r="U8" s="24"/>
     </row>
     <row r="9" ht="106.4" customHeight="true">
@@ -9000,7 +8966,7 @@
       <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-南潢ʒ</t>
+南潢</t>
         </is>
       </c>
       <c r="U9" s="22"/>
@@ -9028,7 +8994,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -9040,20 +9006,20 @@
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -9081,8 +9047,7 @@
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -9090,8 +9055,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -9104,17 +9068,11 @@
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
-      <c r="R11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="R11" s="21"/>
       <c r="S11" s="24"/>
       <c r="T11" s="21"/>
       <c r="U11" s="24"/>
@@ -9135,7 +9093,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -9148,7 +9106,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -9222,17 +9180,9 @@
     </row>
     <row r="14" ht="106.4" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -9240,11 +9190,7 @@
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
@@ -9252,11 +9198,7 @@
         </is>
       </c>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
@@ -9463,12 +9405,7 @@
       <c r="Q22" s="24"/>
       <c r="R22" s="21"/>
       <c r="S22" s="24"/>
-      <c r="T22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="T22" s="21"/>
       <c r="U22" s="24"/>
     </row>
     <row r="23" ht="106.4" customHeight="true">
@@ -9548,8 +9485,7 @@
       <c r="S25" s="24"/>
       <c r="T25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="U25" s="24"/>
@@ -9670,7 +9606,7 @@
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C31" s="22"/>
@@ -9709,7 +9645,7 @@
       <c r="M31" s="22"/>
       <c r="N31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="O31" s="22"/>
@@ -9728,7 +9664,7 @@
       <c r="S31" s="22"/>
       <c r="T31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="U31" s="22"/>
@@ -9767,7 +9703,7 @@
       <c r="O32" s="23"/>
       <c r="P32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="Q32" s="23"/>
@@ -9796,11 +9732,7 @@
       <c r="M33" s="24"/>
       <c r="N33" s="21"/>
       <c r="O33" s="24"/>
-      <c r="P33" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="P33" s="21"/>
       <c r="Q33" s="24"/>
       <c r="R33" s="21"/>
       <c r="S33" s="24"/>
@@ -9824,7 +9756,7 @@
       <c r="E34" s="22"/>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G34" s="22"/>
@@ -9842,7 +9774,7 @@
       <c r="K34" s="22"/>
       <c r="L34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M34" s="22"/>
@@ -9860,7 +9792,7 @@
       <c r="Q34" s="22"/>
       <c r="R34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="S34" s="22"/>
@@ -9916,55 +9848,29 @@
     </row>
     <row r="36" ht="106.4" customHeight="true">
       <c r="A36" s="0"/>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B36" s="21"/>
       <c r="C36" s="24"/>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D36" s="21"/>
       <c r="E36" s="24"/>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-‹</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="G36" s="24"/>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H36" s="21"/>
       <c r="I36" s="24"/>
-      <c r="J36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J36" s="21"/>
       <c r="K36" s="24"/>
       <c r="L36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-‹</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="M36" s="24"/>
-      <c r="N36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N36" s="21"/>
       <c r="O36" s="24"/>
-      <c r="P36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P36" s="21"/>
       <c r="Q36" s="24"/>
       <c r="R36" s="21" t="inlineStr">
         <is>
@@ -9972,11 +9878,7 @@
         </is>
       </c>
       <c r="S36" s="24"/>
-      <c r="T36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T36" s="21"/>
       <c r="U36" s="24"/>
     </row>
     <row r="37" ht="106.4" customHeight="true">
@@ -9989,7 +9891,7 @@
       <c r="C37" s="22"/>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E37" s="22"/>
@@ -10046,7 +9948,7 @@
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C38" s="23"/>
@@ -10059,13 +9961,13 @@
       <c r="E38" s="23"/>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G38" s="23"/>
       <c r="H38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I38" s="23"/>
@@ -10102,7 +10004,7 @@
       <c r="S38" s="23"/>
       <c r="T38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="U38" s="23"/>
@@ -10111,8 +10013,7 @@
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C39" s="24"/>
@@ -10124,15 +10025,13 @@
       <c r="E39" s="24"/>
       <c r="F39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G39" s="24"/>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I39" s="24"/>
@@ -10145,15 +10044,13 @@
       <c r="K39" s="24"/>
       <c r="L39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M39" s="24"/>
       <c r="N39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O39" s="24"/>
@@ -10161,15 +10058,13 @@
       <c r="Q39" s="24"/>
       <c r="R39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="S39" s="24"/>
       <c r="T39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="U39" s="24"/>
@@ -10225,7 +10120,7 @@
       <c r="O40" s="22"/>
       <c r="P40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q40" s="22"/>
@@ -10305,11 +10200,7 @@
     </row>
     <row r="42" ht="106.4" customHeight="true">
       <c r="A42" s="0"/>
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B42" s="21"/>
       <c r="C42" s="24"/>
       <c r="D42" s="21" t="inlineStr">
         <is>
@@ -10317,35 +10208,15 @@
         </is>
       </c>
       <c r="E42" s="24"/>
-      <c r="F42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F42" s="21"/>
       <c r="G42" s="24"/>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H42" s="21"/>
       <c r="I42" s="24"/>
-      <c r="J42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J42" s="21"/>
       <c r="K42" s="24"/>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L42" s="21"/>
       <c r="M42" s="24"/>
-      <c r="N42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N42" s="21"/>
       <c r="O42" s="24"/>
       <c r="P42" s="21" t="inlineStr">
         <is>
@@ -10353,17 +10224,9 @@
         </is>
       </c>
       <c r="Q42" s="24"/>
-      <c r="R42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R42" s="21"/>
       <c r="S42" s="24"/>
-      <c r="T42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T42" s="21"/>
       <c r="U42" s="24"/>
     </row>
     <row r="43" ht="6.0" customHeight="true">
@@ -10421,7 +10284,7 @@
       <c r="Q45" s="22"/>
       <c r="R45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="S45" s="22"/>
@@ -10505,7 +10368,7 @@
       <c r="O48" s="22"/>
       <c r="P48" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="Q48" s="22"/>
@@ -10517,7 +10380,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="U48" s="22"/>
@@ -10569,23 +10432,11 @@
       <c r="M50" s="24"/>
       <c r="N50" s="21"/>
       <c r="O50" s="24"/>
-      <c r="P50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P50" s="21"/>
       <c r="Q50" s="24"/>
-      <c r="R50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R50" s="21"/>
       <c r="S50" s="24"/>
-      <c r="T50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T50" s="21"/>
       <c r="U50" s="24"/>
     </row>
     <row r="51" ht="106.4" customHeight="true">
@@ -10648,7 +10499,7 @@
       <c r="Q52" s="23"/>
       <c r="R52" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="S52" s="23"/>
@@ -10682,11 +10533,7 @@
         </is>
       </c>
       <c r="Q53" s="24"/>
-      <c r="R53" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="R53" s="21"/>
       <c r="S53" s="24"/>
       <c r="T53" s="21" t="inlineStr">
         <is>
@@ -10789,11 +10636,7 @@
         </is>
       </c>
       <c r="Q56" s="24"/>
-      <c r="R56" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R56" s="21"/>
       <c r="S56" s="24"/>
       <c r="T56" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/조재수의 이별 그리고 그리움.xlsx
+++ b/sheets/조재수대금교본/검수/조재수의 이별 그리고 그리움.xlsx
@@ -8648,7 +8648,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -8661,7 +8661,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -8674,7 +8674,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -8687,7 +8687,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -8700,7 +8700,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -8788,7 +8788,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="G6" s="22"/>
@@ -8800,7 +8800,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -8817,18 +8817,22 @@
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 南</t>
         </is>
       </c>
       <c r="S6" s="22"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -8903,7 +8907,11 @@
         </is>
       </c>
       <c r="S8" s="24"/>
-      <c r="T8" s="21"/>
+      <c r="T8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="U8" s="24"/>
     </row>
     <row r="9" ht="106.4" customHeight="true">
@@ -8966,7 +8974,7 @@
       <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-南潢</t>
+南潢ʒ</t>
         </is>
       </c>
       <c r="U9" s="22"/>
@@ -8994,7 +9002,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -9006,20 +9014,20 @@
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -9072,7 +9080,11 @@
         </is>
       </c>
       <c r="Q11" s="24"/>
-      <c r="R11" s="21"/>
+      <c r="R11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="S11" s="24"/>
       <c r="T11" s="21"/>
       <c r="U11" s="24"/>
@@ -9093,7 +9105,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∧</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -9106,7 +9118,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∧</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -9405,7 +9417,11 @@
       <c r="Q22" s="24"/>
       <c r="R22" s="21"/>
       <c r="S22" s="24"/>
-      <c r="T22" s="21"/>
+      <c r="T22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="U22" s="24"/>
     </row>
     <row r="23" ht="106.4" customHeight="true">
@@ -9606,7 +9622,7 @@
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="C31" s="22"/>
@@ -9645,7 +9661,7 @@
       <c r="M31" s="22"/>
       <c r="N31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="O31" s="22"/>
@@ -9664,7 +9680,7 @@
       <c r="S31" s="22"/>
       <c r="T31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="U31" s="22"/>
@@ -9703,7 +9719,7 @@
       <c r="O32" s="23"/>
       <c r="P32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="Q32" s="23"/>
@@ -9732,7 +9748,11 @@
       <c r="M33" s="24"/>
       <c r="N33" s="21"/>
       <c r="O33" s="24"/>
-      <c r="P33" s="21"/>
+      <c r="P33" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="Q33" s="24"/>
       <c r="R33" s="21"/>
       <c r="S33" s="24"/>
@@ -9756,7 +9776,7 @@
       <c r="E34" s="22"/>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∧</t>
         </is>
       </c>
       <c r="G34" s="22"/>
@@ -9774,7 +9794,7 @@
       <c r="K34" s="22"/>
       <c r="L34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∧</t>
         </is>
       </c>
       <c r="M34" s="22"/>
@@ -9792,7 +9812,7 @@
       <c r="Q34" s="22"/>
       <c r="R34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∧</t>
         </is>
       </c>
       <c r="S34" s="22"/>
@@ -9891,7 +9911,7 @@
       <c r="C37" s="22"/>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="E37" s="22"/>
@@ -9948,7 +9968,7 @@
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="C38" s="23"/>
@@ -9961,13 +9981,13 @@
       <c r="E38" s="23"/>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="G38" s="23"/>
       <c r="H38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="I38" s="23"/>
@@ -10004,7 +10024,7 @@
       <c r="S38" s="23"/>
       <c r="T38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="U38" s="23"/>
@@ -10120,7 +10140,7 @@
       <c r="O40" s="22"/>
       <c r="P40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∧</t>
         </is>
       </c>
       <c r="Q40" s="22"/>
@@ -10284,7 +10304,7 @@
       <c r="Q45" s="22"/>
       <c r="R45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="S45" s="22"/>
@@ -10368,7 +10388,7 @@
       <c r="O48" s="22"/>
       <c r="P48" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="Q48" s="22"/>
@@ -10380,7 +10400,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="U48" s="22"/>
@@ -10499,7 +10519,7 @@
       <c r="Q52" s="23"/>
       <c r="R52" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="S52" s="23"/>
@@ -10533,7 +10553,11 @@
         </is>
       </c>
       <c r="Q53" s="24"/>
-      <c r="R53" s="21"/>
+      <c r="R53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="S53" s="24"/>
       <c r="T53" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/조재수의 이별 그리고 그리움.xlsx
+++ b/sheets/조재수대금교본/검수/조재수의 이별 그리고 그리움.xlsx
@@ -8586,32 +8586,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="138.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="138.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="138.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -8772,7 +8772,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="138.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -8878,7 +8878,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="138.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="138.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="138.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="138.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="138.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -9190,7 +9190,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="138.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -9239,7 +9239,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="71.43" customHeight="true">
+    <row r="16" ht="93.02" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="106.4" customHeight="true">
+    <row r="17" ht="138.71" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="106.4" customHeight="true">
+    <row r="18" ht="138.71" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="106.4" customHeight="true">
+    <row r="19" ht="138.71" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -9343,7 +9343,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="106.4" customHeight="true">
+    <row r="20" ht="138.71" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="106.4" customHeight="true">
+    <row r="21" ht="138.71" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="U21" s="23"/>
     </row>
-    <row r="22" ht="106.4" customHeight="true">
+    <row r="22" ht="138.71" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="106.4" customHeight="true">
+    <row r="23" ht="138.71" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="106.4" customHeight="true">
+    <row r="24" ht="138.71" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="U24" s="23"/>
     </row>
-    <row r="25" ht="106.4" customHeight="true">
+    <row r="25" ht="138.71" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="106.4" customHeight="true">
+    <row r="26" ht="138.71" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="106.4" customHeight="true">
+    <row r="27" ht="138.71" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="106.4" customHeight="true">
+    <row r="28" ht="138.71" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -9591,7 +9591,7 @@
     <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="71.43" customHeight="true">
+    <row r="30" ht="93.02" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="106.4" customHeight="true">
+    <row r="31" ht="138.71" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="106.4" customHeight="true">
+    <row r="32" ht="138.71" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="23"/>
@@ -9732,7 +9732,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="23"/>
     </row>
-    <row r="33" ht="106.4" customHeight="true">
+    <row r="33" ht="138.71" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="24"/>
@@ -9759,7 +9759,7 @@
       <c r="T33" s="21"/>
       <c r="U33" s="24"/>
     </row>
-    <row r="34" ht="106.4" customHeight="true">
+    <row r="34" ht="138.71" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="106.4" customHeight="true">
+    <row r="35" ht="138.71" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -9866,7 +9866,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="106.4" customHeight="true">
+    <row r="36" ht="138.71" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -9901,7 +9901,7 @@
       <c r="T36" s="21"/>
       <c r="U36" s="24"/>
     </row>
-    <row r="37" ht="106.4" customHeight="true">
+    <row r="37" ht="138.71" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="106.4" customHeight="true">
+    <row r="38" ht="138.71" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="U38" s="23"/>
     </row>
-    <row r="39" ht="106.4" customHeight="true">
+    <row r="39" ht="138.71" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="U39" s="24"/>
     </row>
-    <row r="40" ht="106.4" customHeight="true">
+    <row r="40" ht="138.71" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="U40" s="22"/>
     </row>
-    <row r="41" ht="106.4" customHeight="true">
+    <row r="41" ht="138.71" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="U41" s="23"/>
     </row>
-    <row r="42" ht="106.4" customHeight="true">
+    <row r="42" ht="138.71" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="24"/>
@@ -10252,7 +10252,7 @@
     <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="71.43" customHeight="true">
+    <row r="44" ht="93.02" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="106.4" customHeight="true">
+    <row r="45" ht="138.71" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="106.4" customHeight="true">
+    <row r="46" ht="138.71" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21"/>
       <c r="C46" s="23"/>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="U46" s="23"/>
     </row>
-    <row r="47" ht="106.4" customHeight="true">
+    <row r="47" ht="138.71" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="24"/>
@@ -10370,7 +10370,7 @@
       <c r="T47" s="21"/>
       <c r="U47" s="24"/>
     </row>
-    <row r="48" ht="106.4" customHeight="true">
+    <row r="48" ht="138.71" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="U48" s="22"/>
     </row>
-    <row r="49" ht="106.4" customHeight="true">
+    <row r="49" ht="138.71" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21"/>
       <c r="C49" s="23"/>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="U49" s="23"/>
     </row>
-    <row r="50" ht="106.4" customHeight="true">
+    <row r="50" ht="138.71" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21"/>
       <c r="C50" s="24"/>
@@ -10459,7 +10459,7 @@
       <c r="T50" s="21"/>
       <c r="U50" s="24"/>
     </row>
-    <row r="51" ht="106.4" customHeight="true">
+    <row r="51" ht="138.71" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21"/>
       <c r="C51" s="22"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="U51" s="22"/>
     </row>
-    <row r="52" ht="106.4" customHeight="true">
+    <row r="52" ht="138.71" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21"/>
       <c r="C52" s="23"/>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="U52" s="23"/>
     </row>
-    <row r="53" ht="106.4" customHeight="true">
+    <row r="53" ht="138.71" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="24"/>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="U53" s="24"/>
     </row>
-    <row r="54" ht="106.4" customHeight="true">
+    <row r="54" ht="138.71" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="U54" s="22"/>
     </row>
-    <row r="55" ht="106.4" customHeight="true">
+    <row r="55" ht="138.71" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="23"/>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="U55" s="23"/>
     </row>
-    <row r="56" ht="106.4" customHeight="true">
+    <row r="56" ht="138.71" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21"/>
       <c r="C56" s="24"/>
@@ -10678,7 +10678,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
